--- a/construction_template/data/templates_blank/progress_schedule.xlsx
+++ b/construction_template/data/templates_blank/progress_schedule.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20377"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\標案\110年度\110203-通河西街碼頭新設船泊工程及社子島迎星碼頭新設船泊工程\110203--招標文件\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9293BA-C035-4DAA-A1C8-F4BC9F319EE0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
@@ -74,7 +72,7 @@
     </r>
   </si>
   <si>
-    <t>臺北市政府工務局水利工程處</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <r>
@@ -109,7 +107,7 @@
     <t>假設工程</t>
   </si>
   <si>
-    <t>施工地點：臺北市士林區</t>
+    <t xml:space="preserve"/>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -126,7 +124,7 @@
   </si>
   <si>
     <r>
-      <t>110</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -135,7 +133,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t>年度</t>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -143,7 +141,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>-111</t>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -152,7 +150,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t>年度</t>
+      <t/>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -168,17 +166,17 @@
     </r>
   </si>
   <si>
-    <t>通河西街碼頭
+    <t xml:space="preserve">
 固定樁工程</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>通河西街碼頭
+    <t xml:space="preserve">
 浮筒組裝工程</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>通河西街碼頭
+    <t xml:space="preserve">
 新舊工程銜接</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -382,7 +380,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>工程名稱：通河西街碼頭新設船泊工程及社子島迎星碼頭新設船泊工程</t>
+    <t xml:space="preserve">工程名稱：</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/construction_template/data/templates_blank/progress_schedule.xlsx
+++ b/construction_template/data/templates_blank/progress_schedule.xlsx
@@ -4,7 +4,9 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20377"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15"/>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
+    </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9293BA-C035-4DAA-A1C8-F4BC9F319EE0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
@@ -72,7 +74,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <r>
@@ -107,7 +109,7 @@
     <t>假設工程</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -124,7 +126,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -380,7 +382,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">工程名稱：</t>
+    <t>工程名稱：</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1331,7 +1333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3066,7 +3068,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -3078,7 +3080,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -3090,7 +3092,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData/>

--- a/construction_template/data/templates_blank/progress_schedule.xlsx
+++ b/construction_template/data/templates_blank/progress_schedule.xlsx
@@ -110,7 +110,6 @@
   </si>
   <si>
     <t/>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>材料訂製</t>
@@ -125,36 +124,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t/>
   </si>
   <si>
     <r>

--- a/construction_template/data/templates_blank/progress_schedule.xlsx
+++ b/construction_template/data/templates_blank/progress_schedule.xlsx
@@ -26,336 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>預定工期</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>日曆天</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>項</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>次</t>
-    </r>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>工程編號：</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>預 定 進 度 表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>年度</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>主要工作項目</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">     日期天數</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>假設工程</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>材料訂製</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>八</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>辦理時間</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>日數</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">
-固定樁工程</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-浮筒組裝工程</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-新舊工程銜接</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>迎星碼頭
-固定樁工程</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>迎星碼頭
-浮筒組裝工程</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>迎星碼頭
-新舊工程銜接</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>一</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>二</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>三</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>四</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>五</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>六</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>七</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>日曆天</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>日曆天</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>日曆天</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>日曆天</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>工程名稱：</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1320,9 +991,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:42" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="67" t="s">
-        <v>4</v>
-      </c>
+      <c r="A2" s="67"/>
       <c r="B2" s="67"/>
       <c r="C2" s="67"/>
       <c r="D2" s="67"/>
@@ -1362,8 +1031,10 @@
       <c r="AL2" s="67"/>
     </row>
     <row r="3" spans="1:42" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
-        <v>6</v>
+      <c r="A3" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">預 定 進 度 表</t>
+        </is>
       </c>
       <c r="B3" s="67"/>
       <c r="C3" s="67"/>
@@ -1444,8 +1115,10 @@
       <c r="AL4" s="67"/>
     </row>
     <row r="5" spans="1:42" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
-        <v>34</v>
+      <c r="A5" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程名稱：${project.name}</t>
+        </is>
       </c>
       <c r="B5" s="69"/>
       <c r="C5" s="69"/>
@@ -1486,15 +1159,15 @@
       <c r="AL5" s="69"/>
     </row>
     <row r="6" spans="1:42" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68" t="s">
-        <v>11</v>
-      </c>
+      <c r="A6" s="68"/>
       <c r="B6" s="69"/>
       <c r="C6" s="69"/>
       <c r="D6" s="69"/>
       <c r="E6" s="69"/>
-      <c r="F6" s="69" t="s">
-        <v>5</v>
+      <c r="F6" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程編號：</t>
+        </is>
       </c>
       <c r="G6" s="69"/>
       <c r="H6" s="69"/>
@@ -1570,14 +1243,22 @@
       <c r="AL7" s="67"/>
     </row>
     <row r="8" spans="1:42" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
-        <v>0</v>
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">預定工期</t>
+        </is>
       </c>
-      <c r="B8" s="18"/>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${plannedDuration}</t>
+        </is>
+      </c>
       <c r="C8" s="19"/>
       <c r="D8" s="16"/>
-      <c r="E8" s="20" t="s">
-        <v>1</v>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日曆天</t>
+        </is>
       </c>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
@@ -1659,15 +1340,21 @@
     </row>
     <row r="10" spans="1:42" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
-      <c r="B10" s="10" t="s">
-        <v>2</v>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">項</t>
+        </is>
       </c>
-      <c r="C10" s="70" t="s">
-        <v>7</v>
+      <c r="C10" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">年度</t>
+        </is>
       </c>
       <c r="D10" s="71"/>
-      <c r="E10" s="37" t="s">
-        <v>14</v>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辦理時間</t>
+        </is>
       </c>
       <c r="F10" s="38"/>
       <c r="G10" s="38"/>
@@ -1706,13 +1393,13 @@
     <row r="11" spans="1:42" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="11"/>
-      <c r="C11" s="72" t="s">
-        <v>9</v>
+      <c r="C11" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     日期天數</t>
+        </is>
       </c>
       <c r="D11" s="73"/>
-      <c r="E11" s="40" t="s">
-        <v>15</v>
-      </c>
+      <c r="E11" s="40"/>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
       <c r="H11" s="38"/>
@@ -1749,15 +1436,21 @@
     </row>
     <row r="12" spans="1:42" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
-      <c r="B12" s="12" t="s">
-        <v>3</v>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">次</t>
+        </is>
       </c>
-      <c r="C12" s="74" t="s">
-        <v>8</v>
+      <c r="C12" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要工作項目</t>
+        </is>
       </c>
       <c r="D12" s="75"/>
-      <c r="E12" s="34" t="s">
-        <v>16</v>
+      <c r="E12" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日數</t>
+        </is>
       </c>
       <c r="F12" s="35"/>
       <c r="G12" s="36"/>
@@ -1795,16 +1488,10 @@
     </row>
     <row r="13" spans="1:42" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
-      <c r="B13" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="64" t="s">
-        <v>10</v>
-      </c>
+      <c r="B13" s="50"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="13"/>
-      <c r="E13" s="44" t="s">
-        <v>30</v>
-      </c>
+      <c r="E13" s="44"/>
       <c r="F13" s="22"/>
       <c r="G13" s="23"/>
       <c r="H13" s="22"/>
@@ -1921,16 +1608,10 @@
     </row>
     <row r="16" spans="1:42" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
-      <c r="B16" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="64" t="s">
-        <v>12</v>
-      </c>
+      <c r="B16" s="50"/>
+      <c r="C16" s="64"/>
       <c r="D16" s="13"/>
-      <c r="E16" s="44" t="s">
-        <v>31</v>
-      </c>
+      <c r="E16" s="44"/>
       <c r="F16" s="22"/>
       <c r="G16" s="23"/>
       <c r="H16" s="22"/>
@@ -2047,16 +1728,10 @@
     </row>
     <row r="19" spans="1:38" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
-      <c r="B19" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>17</v>
-      </c>
+      <c r="B19" s="50"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="13"/>
-      <c r="E19" s="44" t="s">
-        <v>32</v>
-      </c>
+      <c r="E19" s="44"/>
       <c r="F19" s="22"/>
       <c r="G19" s="23"/>
       <c r="H19" s="22"/>
@@ -2173,16 +1848,10 @@
     </row>
     <row r="22" spans="1:38" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
-      <c r="B22" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>18</v>
-      </c>
+      <c r="B22" s="50"/>
+      <c r="C22" s="41"/>
       <c r="D22" s="13"/>
-      <c r="E22" s="44" t="s">
-        <v>31</v>
-      </c>
+      <c r="E22" s="44"/>
       <c r="F22" s="22"/>
       <c r="G22" s="23"/>
       <c r="H22" s="22"/>
@@ -2299,16 +1968,10 @@
     </row>
     <row r="25" spans="1:38" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
-      <c r="B25" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>19</v>
-      </c>
+      <c r="B25" s="50"/>
+      <c r="C25" s="41"/>
       <c r="D25" s="13"/>
-      <c r="E25" s="44" t="s">
-        <v>30</v>
-      </c>
+      <c r="E25" s="44"/>
       <c r="F25" s="22"/>
       <c r="G25" s="23"/>
       <c r="H25" s="22"/>
@@ -2425,16 +2088,10 @@
     </row>
     <row r="28" spans="1:38" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
-      <c r="B28" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>20</v>
-      </c>
+      <c r="B28" s="53"/>
+      <c r="C28" s="41"/>
       <c r="D28" s="13"/>
-      <c r="E28" s="44" t="s">
-        <v>30</v>
-      </c>
+      <c r="E28" s="44"/>
       <c r="F28" s="22"/>
       <c r="G28" s="23"/>
       <c r="H28" s="22"/>
@@ -2551,16 +2208,10 @@
     </row>
     <row r="31" spans="1:38" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
-      <c r="B31" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="61" t="s">
-        <v>21</v>
-      </c>
+      <c r="B31" s="53"/>
+      <c r="C31" s="61"/>
       <c r="D31" s="13"/>
-      <c r="E31" s="44" t="s">
-        <v>31</v>
-      </c>
+      <c r="E31" s="44"/>
       <c r="F31" s="22"/>
       <c r="G31" s="23"/>
       <c r="H31" s="22"/>
@@ -2677,16 +2328,10 @@
     </row>
     <row r="34" spans="1:42" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9"/>
-      <c r="B34" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>22</v>
-      </c>
+      <c r="B34" s="53"/>
+      <c r="C34" s="41"/>
       <c r="D34" s="13"/>
-      <c r="E34" s="54" t="s">
-        <v>33</v>
-      </c>
+      <c r="E34" s="54"/>
       <c r="F34" s="22"/>
       <c r="G34" s="23"/>
       <c r="H34" s="22"/>
